--- a/data/trending_integrated_20260922_13.xlsx
+++ b/data/trending_integrated_20260922_13.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51997721690</v>
+        <v>52058155690</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5428119164</v>
+        <v>5428947159</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66000</v>
+        <v>65500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+26.20%</t>
+          <t>'+25.24%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>159480378800</v>
+        <v>161087898750</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -803,23 +803,23 @@
         <v>16300</v>
       </c>
       <c r="R4" t="n">
-        <v>-2000</v>
+        <v>-15000</v>
       </c>
       <c r="S4" t="n">
-        <v>49000</v>
+        <v>40000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브로드컴 공급 계약 관련 긍정적 뉴스 및 반도체 섹터 키맞추기 기대감. 높은 단기 상승률.</t>
+          <t>브로드컴 투자 공급 계약 관련 긍정적 반응. 키 맞추기 및 이격 축소 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['브로드컴', '공급계약', '키맞추기']</t>
+          <t>['브로드컴', '공급 계약', '키 맞추기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13030</v>
+        <v>13140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.18%</t>
+          <t>'+18.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>164800756500</v>
+        <v>169666763280</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114500</v>
+        <v>113700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.37%</t>
+          <t>'+11.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>278445470000</v>
+        <v>280991780750</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -990,7 +990,7 @@
         <v>234000</v>
       </c>
       <c r="S6" t="n">
-        <v>14000</v>
+        <v>24000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32400</v>
+        <v>32150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.09%</t>
+          <t>'+8.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>242277736425</v>
+        <v>244824321575</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1082,20 +1082,20 @@
         <v>262000</v>
       </c>
       <c r="S7" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 전력 수요 증가 관련 기대감 속 신고점 돌파 시도. 가온전선과의 비교 언급.</t>
+          <t>가온전선과의 비교 속 대한전선 주가 부진. 외인·기관 매도 시작.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '전력 수요', '신고점']</t>
+          <t>['대한전선', '가온전선', '주가 부진']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30750</v>
+        <v>30800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.59%</t>
+          <t>'+6.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,10 +1136,10 @@
         <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H8" t="n">
-        <v>52.05</v>
+        <v>52.11</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>29250</v>
       </c>
       <c r="L8" t="n">
-        <v>30750</v>
+        <v>30850</v>
       </c>
       <c r="M8" t="n">
         <v>29150</v>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>95542287075</v>
+        <v>106870040875</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1174,7 +1174,7 @@
         <v>324000</v>
       </c>
       <c r="S8" t="n">
-        <v>118000</v>
+        <v>265000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>-0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G9" t="n">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="H9" t="n">
         <v>10.47</v>
@@ -1254,7 +1254,7 @@
         <v>10.74</v>
       </c>
       <c r="O9" t="n">
-        <v>119394288845</v>
+        <v>127172402690</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1266,11 +1266,11 @@
         <v>-76000</v>
       </c>
       <c r="S9" t="n">
-        <v>9000</v>
+        <v>41000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 세력과의 갈등 및 주가 조작 의혹 제기. 연기금 투입 확인.</t>
+          <t>공매도 세력과의 전쟁 속 주가 상승 시도. 감사원 신고 및 대차 해지 요구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '시세조종', '연기금']</t>
+          <t>['공매도', '주가 상승', '감사원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6120</v>
+        <v>6110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.44%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.19</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0.19</v>
       </c>
       <c r="O10" t="n">
-        <v>64588329055</v>
+        <v>64831007300</v>
       </c>
       <c r="P10" t="n">
         <v>13140</v>
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215500</v>
+        <v>6550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.61%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>298</v>
+        <v>163</v>
       </c>
       <c r="H11" t="n">
-        <v>75.5</v>
+        <v>4.86</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>208000</v>
+        <v>6310</v>
       </c>
       <c r="K11" t="n">
-        <v>215000</v>
+        <v>6460</v>
       </c>
       <c r="L11" t="n">
-        <v>216000</v>
+        <v>7090</v>
       </c>
       <c r="M11" t="n">
-        <v>211000</v>
+        <v>6350</v>
       </c>
       <c r="N11" t="n">
-        <v>75.44</v>
+        <v>4.95</v>
       </c>
       <c r="O11" t="n">
-        <v>645875611250</v>
+        <v>50368464115</v>
       </c>
       <c r="P11" t="n">
-        <v>243500</v>
+        <v>11760</v>
       </c>
       <c r="Q11" t="n">
-        <v>64700</v>
+        <v>1620</v>
       </c>
       <c r="R11" t="n">
-        <v>-691000</v>
+        <v>-92000</v>
       </c>
       <c r="S11" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6510</v>
+        <v>214500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.17%</t>
+          <t>'+3.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>167</v>
+        <v>326</v>
       </c>
       <c r="H12" t="n">
-        <v>4.86</v>
+        <v>75.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6310</v>
+        <v>208000</v>
       </c>
       <c r="K12" t="n">
-        <v>6460</v>
+        <v>215000</v>
       </c>
       <c r="L12" t="n">
-        <v>7090</v>
+        <v>216000</v>
       </c>
       <c r="M12" t="n">
-        <v>6350</v>
+        <v>211000</v>
       </c>
       <c r="N12" t="n">
-        <v>4.95</v>
+        <v>75.44</v>
       </c>
       <c r="O12" t="n">
-        <v>50055803845</v>
+        <v>673221760750</v>
       </c>
       <c r="P12" t="n">
-        <v>11760</v>
+        <v>243500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1620</v>
+        <v>64700</v>
       </c>
       <c r="R12" t="n">
-        <v>-92000</v>
+        <v>-683000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-90000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>328500</v>
+        <v>13310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="H13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>318500</v>
+        <v>12960</v>
       </c>
       <c r="K13" t="n">
-        <v>333000</v>
+        <v>13500</v>
       </c>
       <c r="L13" t="n">
-        <v>349500</v>
+        <v>14190</v>
       </c>
       <c r="M13" t="n">
-        <v>325000</v>
+        <v>13250</v>
       </c>
       <c r="N13" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>109274203750</v>
+        <v>20738563905</v>
       </c>
       <c r="P13" t="n">
-        <v>635000</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>52600</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-8000</v>
+        <v>-46000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>신고가 경신 및 52주 신고가 돌파 기대감. 모더나, 텍사스 가스복합발전 프로젝트 테마 연관성 언급. 외인 지분율 상승.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['신고가', '테마주', '외인지분율']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13910</v>
+        <v>326500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="H14" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13540</v>
+        <v>318500</v>
       </c>
       <c r="K14" t="n">
-        <v>13870</v>
+        <v>333000</v>
       </c>
       <c r="L14" t="n">
-        <v>14650</v>
+        <v>349500</v>
       </c>
       <c r="M14" t="n">
-        <v>13740</v>
+        <v>325000</v>
       </c>
       <c r="N14" t="n">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="O14" t="n">
-        <v>88863036410</v>
+        <v>110469192750</v>
       </c>
       <c r="P14" t="n">
-        <v>20300</v>
+        <v>635000</v>
       </c>
       <c r="Q14" t="n">
-        <v>2885</v>
+        <v>52600</v>
       </c>
       <c r="R14" t="n">
-        <v>18000</v>
+        <v>-7000</v>
       </c>
       <c r="S14" t="n">
         <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>신고가 경신 및 52주 신고가 구간 진입. 텍사스 가스복합발전 프로젝트 수혜 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['신고가', '가스복합발전', '프로젝트']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,43 +1747,43 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13270</v>
+        <v>13850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="E15" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>322</v>
+        <v>169</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12960</v>
+        <v>13540</v>
       </c>
       <c r="K15" t="n">
-        <v>13500</v>
+        <v>13870</v>
       </c>
       <c r="L15" t="n">
-        <v>14190</v>
+        <v>14650</v>
       </c>
       <c r="M15" t="n">
-        <v>13250</v>
+        <v>13740</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O15" t="n">
-        <v>20394141955</v>
+        <v>90265796585</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>20300</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>2885</v>
       </c>
       <c r="R15" t="n">
-        <v>-41000</v>
+        <v>18000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>280500</v>
+        <v>280250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G16" t="n">
-        <v>2071</v>
+        <v>2081</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1898,7 +1898,7 @@
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>2632580187000</v>
+        <v>2714989991750</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1910,11 +1910,11 @@
         <v>-116000</v>
       </c>
       <c r="S16" t="n">
-        <v>128000</v>
+        <v>307000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 낙관론에 따른 주가 상승 기대감 및 배당금 기대감이 혼재. 외인·기관 매수세 유입.</t>
+          <t>AI 낙관론에 따른 주가 상승 기대감 속 배당금 관련 논의. 외인·기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86800</v>
+        <v>86900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.76%</t>
+          <t>'+1.88%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F17" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G17" t="n">
-        <v>1203</v>
+        <v>1218</v>
       </c>
       <c r="H17" t="n">
         <v>23.05</v>
@@ -1981,7 +1981,7 @@
         <v>87000</v>
       </c>
       <c r="L17" t="n">
-        <v>87100</v>
+        <v>87500</v>
       </c>
       <c r="M17" t="n">
         <v>85200</v>
@@ -1990,7 +1990,7 @@
         <v>23.12</v>
       </c>
       <c r="O17" t="n">
-        <v>136617436100</v>
+        <v>152085621300</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -1999,23 +1999,23 @@
         <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>-200000</v>
+        <v>-240000</v>
       </c>
       <c r="S17" t="n">
-        <v>-4000</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대미 투자 SMR 추진 확정 관련 긍정적 전망. 공급 계약 체결 사실 언급.</t>
+          <t>미국 SMR(소형모듈원자로) 사업 추진 확정. 공급 계약 체결 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '대미투자', '공급계약']</t>
+          <t>['SMR', '미국 투자', '공급 계약']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1898000</v>
+        <v>1895000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+1.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G18" t="n">
-        <v>2151</v>
+        <v>2162</v>
       </c>
       <c r="H18" t="n">
         <v>50.17</v>
@@ -2076,13 +2076,13 @@
         <v>1935000</v>
       </c>
       <c r="M18" t="n">
-        <v>1898000</v>
+        <v>1890000</v>
       </c>
       <c r="N18" t="n">
         <v>50.23</v>
       </c>
       <c r="O18" t="n">
-        <v>3032586373500</v>
+        <v>3163884523500</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2091,10 +2091,10 @@
         <v>333000</v>
       </c>
       <c r="R18" t="n">
-        <v>82000</v>
+        <v>44000</v>
       </c>
       <c r="S18" t="n">
-        <v>44000</v>
+        <v>31000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17880</v>
+        <v>17800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.90%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F19" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>736</v>
+        <v>753</v>
       </c>
       <c r="H19" t="n">
         <v>6.22</v>
@@ -2174,7 +2174,7 @@
         <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>143692355055</v>
+        <v>145085878320</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10600</v>
+        <v>10570</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.01</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
         <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H20" t="n">
         <v>9.609999999999999</v>
@@ -2266,7 +2266,7 @@
         <v>8.6</v>
       </c>
       <c r="O20" t="n">
-        <v>125829802105</v>
+        <v>127309005215</v>
       </c>
       <c r="P20" t="n">
         <v>11640</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8550</v>
+        <v>8530</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="H21" t="n">
         <v>26.58</v>
@@ -2358,7 +2358,7 @@
         <v>26.57</v>
       </c>
       <c r="O21" t="n">
-        <v>17085417420</v>
+        <v>17368124430</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2367,23 +2367,23 @@
         <v>8120</v>
       </c>
       <c r="R21" t="n">
-        <v>-418000</v>
+        <v>-436000</v>
       </c>
       <c r="S21" t="n">
-        <v>18000</v>
+        <v>72000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 개선 및 기술 혁신에 따른 장기적 가치 상승 가능성 언급. 대차잔고 감소.</t>
+          <t>적자 회사로 인한 주가 부진. 삼성전자·SK하이닉스와의 비교 속 성장 동력 부재 지적.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적', '기술 혁신', '대차잔고']</t>
+          <t>['적자', '주가 부진', '성장 동력']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21500</v>
+        <v>21400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
         <v>40</v>
       </c>
       <c r="G22" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H22" t="n">
         <v>1.2</v>
@@ -2450,7 +2450,7 @@
         <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>49400298875</v>
+        <v>49993869950</v>
       </c>
       <c r="P22" t="n">
         <v>22900</v>
@@ -2499,18 +2499,18 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24200</v>
+        <v>24150</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
         <v>57</v>
@@ -2542,7 +2542,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>97199729625</v>
+        <v>97848088525</v>
       </c>
       <c r="P23" t="n">
         <v>39350</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3860</v>
+        <v>3825</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.81%</t>
+          <t>'-5.67%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.63</v>
       </c>
       <c r="E24" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H24" t="n">
         <v>0.96</v>
@@ -2634,7 +2634,7 @@
         <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>10056709622</v>
+        <v>10449753832</v>
       </c>
       <c r="P24" t="n">
         <v>6480</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10380</v>
+        <v>10410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-6.15%</t>
+          <t>'-5.88%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>57</v>
       </c>
       <c r="G25" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>37158335475</v>
+        <v>37573735760</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>투자경고 지정 및 하한가 가능성 언급. 단기 급등락에 대한 경계.</t>
+          <t>투자 경고 종목 지정 후 주가 하락. 단주치기 및 개미 꼬시기 의혹 제기.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['투자경고', '급등락', '저점']</t>
+          <t>['투자경고', '주가 하락', '단주치기']</t>
         </is>
       </c>
       <c r="X25" t="n">

--- a/data/trending_integrated_20260922_13.xlsx
+++ b/data/trending_integrated_20260922_13.xlsx
@@ -581,10 +581,10 @@
         <v>141</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52058155690</v>
+        <v>52298268090</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -619,7 +619,7 @@
         <v>15130</v>
       </c>
       <c r="R2" t="n">
-        <v>138000</v>
+        <v>170000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5428947159</v>
+        <v>5430992624</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65500</v>
+        <v>65300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.24%</t>
+          <t>'+24.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>161087898750</v>
+        <v>162227618950</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13140</v>
+        <v>13620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+18.17%</t>
+          <t>'+22.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G5" t="n">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -877,7 +877,7 @@
         <v>11270</v>
       </c>
       <c r="L5" t="n">
-        <v>13610</v>
+        <v>13680</v>
       </c>
       <c r="M5" t="n">
         <v>10810</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>169666763280</v>
+        <v>188495856190</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -895,23 +895,23 @@
         <v>4020</v>
       </c>
       <c r="R5" t="n">
-        <v>17000</v>
+        <v>-24000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>급등 후 하락 및 사기꾼, 개잡주 등 부정적 평가. 대미 투자 1호 가스 발전 관련 내용 언급.</t>
+          <t>가스터빈 관련 대미 투자 소식에도 불구하고 주가 하한가 및 급락세. 이해 불가 의견.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['급등', '하락', '개잡주']</t>
+          <t>['가스터빈', '대미 투자', '주가 급락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>113700</v>
+        <v>112800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.58%</t>
+          <t>'+10.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>280991780750</v>
+        <v>284784836850</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32150</v>
+        <v>31950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.25%</t>
+          <t>'+7.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>244824321575</v>
+        <v>248839143675</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1079,23 +1079,23 @@
         <v>15000</v>
       </c>
       <c r="R7" t="n">
-        <v>262000</v>
+        <v>207000</v>
       </c>
       <c r="S7" t="n">
         <v>7000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 대한전선 주가 부진. 외인·기관 매도 시작.</t>
+          <t>AI 전력 수요 증가에 따른 주목 가능성 언급. 단기 상승 기대감 있으나 전고점 돌파 난항.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['대한전선', '가온전선', '주가 부진']</t>
+          <t>['AI 전력', '거래량', '전고점']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,27 +1119,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30800</v>
+        <v>30950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.76%</t>
+          <t>'+7.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="H8" t="n">
-        <v>52.11</v>
+        <v>52.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>29250</v>
       </c>
       <c r="L8" t="n">
-        <v>30850</v>
+        <v>31000</v>
       </c>
       <c r="M8" t="n">
         <v>29150</v>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>106870040875</v>
+        <v>119708024450</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1171,7 +1171,7 @@
         <v>21000</v>
       </c>
       <c r="R8" t="n">
-        <v>324000</v>
+        <v>872000</v>
       </c>
       <c r="S8" t="n">
         <v>265000</v>
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19160</v>
+        <v>6120</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.76%</t>
+          <t>'+4.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.27</v>
+        <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>655</v>
+        <v>142</v>
       </c>
       <c r="H9" t="n">
-        <v>10.47</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18290</v>
+        <v>5860</v>
       </c>
       <c r="K9" t="n">
-        <v>18830</v>
+        <v>6200</v>
       </c>
       <c r="L9" t="n">
-        <v>19540</v>
+        <v>6610</v>
       </c>
       <c r="M9" t="n">
-        <v>18540</v>
+        <v>6080</v>
       </c>
       <c r="N9" t="n">
-        <v>10.74</v>
+        <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>127172402690</v>
+        <v>65088238130</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>13140</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>3725</v>
       </c>
       <c r="R9" t="n">
-        <v>-76000</v>
+        <v>-259000</v>
       </c>
       <c r="S9" t="n">
-        <v>41000</v>
+        <v>34000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 세력과의 전쟁 속 주가 상승 시도. 감사원 신고 및 대차 해지 요구.</t>
+          <t>가상화폐 테마 강세 및 비트코인 급등에 따른 수혜 기대. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '주가 상승', '감사원']</t>
+          <t>['가상화폐', '비트코인', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6110</v>
+        <v>19030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G10" t="n">
-        <v>141</v>
+        <v>676</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>10.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5860</v>
+        <v>18290</v>
       </c>
       <c r="K10" t="n">
-        <v>6200</v>
+        <v>18830</v>
       </c>
       <c r="L10" t="n">
-        <v>6610</v>
+        <v>19540</v>
       </c>
       <c r="M10" t="n">
-        <v>6080</v>
+        <v>18540</v>
       </c>
       <c r="N10" t="n">
-        <v>0.19</v>
+        <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>64831007300</v>
+        <v>131028749915</v>
       </c>
       <c r="P10" t="n">
-        <v>13140</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3725</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>48000</v>
+        <v>146000</v>
       </c>
       <c r="S10" t="n">
-        <v>27000</v>
+        <v>41000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>가상화폐 테마 강세 및 비트코인 급등에 따른 수혜 기대. 공매도 세력에 대한 언급.</t>
+          <t>공매도 관련 이슈 및 감사원 신고 완료 내용 언급. 연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['가상화폐', '비트코인', '공매도']</t>
+          <t>['공매도', '감사원', '연기금']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6550</v>
+        <v>6490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+2.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,7 +1409,7 @@
         <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
         <v>163</v>
@@ -1438,7 +1438,7 @@
         <v>4.95</v>
       </c>
       <c r="O11" t="n">
-        <v>50368464115</v>
+        <v>51322655710</v>
       </c>
       <c r="P11" t="n">
         <v>11760</v>
@@ -1447,7 +1447,7 @@
         <v>1620</v>
       </c>
       <c r="R11" t="n">
-        <v>-92000</v>
+        <v>-74000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214500</v>
+        <v>213500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.12%</t>
+          <t>'+2.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="H12" t="n">
         <v>75.5</v>
@@ -1530,7 +1530,7 @@
         <v>75.44</v>
       </c>
       <c r="O12" t="n">
-        <v>673221760750</v>
+        <v>699419643000</v>
       </c>
       <c r="P12" t="n">
         <v>243500</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13310</v>
+        <v>326250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>318500</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>333000</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>349500</v>
       </c>
       <c r="M13" t="n">
-        <v>13250</v>
+        <v>325000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O13" t="n">
-        <v>20738563905</v>
+        <v>111843025250</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>635000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>52600</v>
       </c>
       <c r="R13" t="n">
-        <v>-46000</v>
+        <v>-7000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>신고가 경신 및 52주 신고가 구간 진입. 텍사스 가스복합발전 프로젝트 수혜 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['신고가', '가스복합발전', '프로젝트']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>326500</v>
+        <v>13260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.31%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="H14" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>318500</v>
+        <v>12960</v>
       </c>
       <c r="K14" t="n">
-        <v>333000</v>
+        <v>13500</v>
       </c>
       <c r="L14" t="n">
-        <v>349500</v>
+        <v>14190</v>
       </c>
       <c r="M14" t="n">
-        <v>325000</v>
+        <v>13250</v>
       </c>
       <c r="N14" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>110469192750</v>
+        <v>20948970515</v>
       </c>
       <c r="P14" t="n">
-        <v>635000</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>52600</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-7000</v>
+        <v>-46000</v>
       </c>
       <c r="S14" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신고가 경신 및 52주 신고가 구간 진입. 텍사스 가스복합발전 프로젝트 수혜 기대.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신고가', '가스복합발전', '프로젝트']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13850</v>
+        <v>279750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+2.10%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.34</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>481</v>
       </c>
       <c r="G15" t="n">
-        <v>169</v>
+        <v>2107</v>
       </c>
       <c r="H15" t="n">
-        <v>3.34</v>
+        <v>46.56</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13540</v>
+        <v>274000</v>
       </c>
       <c r="K15" t="n">
-        <v>13870</v>
+        <v>283000</v>
       </c>
       <c r="L15" t="n">
-        <v>14650</v>
+        <v>283500</v>
       </c>
       <c r="M15" t="n">
-        <v>13740</v>
+        <v>278500</v>
       </c>
       <c r="N15" t="n">
-        <v>3.68</v>
+        <v>46.46</v>
       </c>
       <c r="O15" t="n">
-        <v>90265796585</v>
+        <v>2821530929500</v>
       </c>
       <c r="P15" t="n">
-        <v>20300</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>2885</v>
+        <v>81100</v>
       </c>
       <c r="R15" t="n">
-        <v>18000</v>
+        <v>550000</v>
       </c>
       <c r="S15" t="n">
-        <v>13000</v>
+        <v>307000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>AI 낙관론 및 배당 기대감에 따른 주가 상승 전망. 외인 및 기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['AI', '배당금', '낙관론']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>280250</v>
+        <v>13760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.28%</t>
+          <t>'+1.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>-0.34</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>482</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>2081</v>
+        <v>176</v>
       </c>
       <c r="H16" t="n">
-        <v>46.56</v>
+        <v>3.34</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>274000</v>
+        <v>13540</v>
       </c>
       <c r="K16" t="n">
-        <v>283000</v>
+        <v>13870</v>
       </c>
       <c r="L16" t="n">
-        <v>283500</v>
+        <v>14650</v>
       </c>
       <c r="M16" t="n">
-        <v>278500</v>
+        <v>13740</v>
       </c>
       <c r="N16" t="n">
-        <v>46.46</v>
+        <v>3.68</v>
       </c>
       <c r="O16" t="n">
-        <v>2714989991750</v>
+        <v>91988064445</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>20300</v>
       </c>
       <c r="Q16" t="n">
-        <v>81100</v>
+        <v>2885</v>
       </c>
       <c r="R16" t="n">
-        <v>-116000</v>
+        <v>8000</v>
       </c>
       <c r="S16" t="n">
-        <v>307000</v>
+        <v>13000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 낙관론에 따른 주가 상승 기대감 속 배당금 관련 논의. 외인·기관 매수세 유입.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI', '배당금', '낙관론']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86900</v>
+        <v>86600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.88%</t>
+          <t>'+1.52%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F17" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G17" t="n">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="H17" t="n">
         <v>23.05</v>
@@ -1990,7 +1990,7 @@
         <v>23.12</v>
       </c>
       <c r="O17" t="n">
-        <v>152085621300</v>
+        <v>158866750250</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1895000</v>
+        <v>1886000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.45%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G18" t="n">
-        <v>2162</v>
+        <v>2121</v>
       </c>
       <c r="H18" t="n">
         <v>50.17</v>
@@ -2076,13 +2076,13 @@
         <v>1935000</v>
       </c>
       <c r="M18" t="n">
-        <v>1890000</v>
+        <v>1882000</v>
       </c>
       <c r="N18" t="n">
         <v>50.23</v>
       </c>
       <c r="O18" t="n">
-        <v>3163884523500</v>
+        <v>3313319364000</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>AI 개발 관련 긍정적 뉴스에도 불구하고 주가 등락 혼조. 전고점 돌파 및 200만원 돌파 기대.</t>
+          <t>AI 수요 증가에 따른 SK하이닉스 주가 상승 기대. 200 돌파 및 25만원 목표.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['AI', '전고점', '자사주']</t>
+          <t>['AI', 'SK하이닉스', '자사주 매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17800</v>
+        <v>17790</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19" t="n">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="H19" t="n">
         <v>6.22</v>
@@ -2174,7 +2174,7 @@
         <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>145085878320</v>
+        <v>146385102450</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2183,10 +2183,10 @@
         <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-545000</v>
+        <v>-494000</v>
       </c>
       <c r="S19" t="n">
-        <v>7000</v>
+        <v>14000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10570</v>
+        <v>10590</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.01</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
         <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H20" t="n">
         <v>9.609999999999999</v>
@@ -2266,7 +2266,7 @@
         <v>8.6</v>
       </c>
       <c r="O20" t="n">
-        <v>127309005215</v>
+        <v>128914328750</v>
       </c>
       <c r="P20" t="n">
         <v>11640</v>
@@ -2275,10 +2275,10 @@
         <v>3735</v>
       </c>
       <c r="R20" t="n">
-        <v>209000</v>
+        <v>215000</v>
       </c>
       <c r="S20" t="n">
-        <v>-38000</v>
+        <v>-478000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8530</v>
+        <v>8490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="H21" t="n">
         <v>26.58</v>
@@ -2358,7 +2358,7 @@
         <v>26.57</v>
       </c>
       <c r="O21" t="n">
-        <v>17368124430</v>
+        <v>17944816395</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>적자 회사로 인한 주가 부진. 삼성전자·SK하이닉스와의 비교 속 성장 동력 부재 지적.</t>
+          <t>LG디스플레이의 주가 부진에 대한 논의. 반도체 늪, 무능한 회사라는 평가.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['적자', '주가 부진', '성장 동력']</t>
+          <t>['LG디스플레이', '주가 부진', '재무 실적']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="H22" t="n">
         <v>1.2</v>
@@ -2450,7 +2450,7 @@
         <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>49993869950</v>
+        <v>50387222300</v>
       </c>
       <c r="P22" t="n">
         <v>22900</v>
@@ -2459,10 +2459,10 @@
         <v>9900</v>
       </c>
       <c r="R22" t="n">
-        <v>47000</v>
+        <v>79000</v>
       </c>
       <c r="S22" t="n">
-        <v>-3000</v>
+        <v>-8000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2499,18 +2499,18 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24150</v>
+        <v>24100</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" t="n">
         <v>57</v>
@@ -2542,7 +2542,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>97848088525</v>
+        <v>98553079125</v>
       </c>
       <c r="P23" t="n">
         <v>39350</v>
@@ -2551,7 +2551,7 @@
         <v>8200</v>
       </c>
       <c r="R23" t="n">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2587,70 +2587,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3825</v>
+        <v>10400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.67%</t>
+          <t>'-5.97%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G24" t="n">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="H24" t="n">
-        <v>0.96</v>
+        <v>17.89</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>4055</v>
+        <v>11060</v>
       </c>
       <c r="K24" t="n">
-        <v>4080</v>
+        <v>10570</v>
       </c>
       <c r="L24" t="n">
-        <v>4080</v>
+        <v>10815</v>
       </c>
       <c r="M24" t="n">
-        <v>3825</v>
+        <v>10060</v>
       </c>
       <c r="N24" t="n">
-        <v>0.33</v>
+        <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>10449753832</v>
+        <v>37930908415</v>
       </c>
       <c r="P24" t="n">
-        <v>6480</v>
+        <v>22450</v>
       </c>
       <c r="Q24" t="n">
-        <v>1738</v>
+        <v>1760</v>
       </c>
       <c r="R24" t="n">
-        <v>51000</v>
+        <v>-11000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>급락 및 하한가 가능성 언급. 선수 이탈 및 신용 물량 털기에 대한 부정적 전망.</t>
+          <t>투자경고 종목 지정 및 주가 하락세. 조급해하지 말라는 의견.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['급락', '하한가', '신용']</t>
+          <t>['투경', '단주치기', '주가 하락']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,90 +2672,90 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10410</v>
+        <v>3810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-6.04%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E25" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G25" t="n">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="H25" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K25" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L25" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M25" t="n">
-        <v>10060</v>
+        <v>3810</v>
       </c>
       <c r="N25" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O25" t="n">
-        <v>37573735760</v>
+        <v>10794555732</v>
       </c>
       <c r="P25" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q25" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R25" t="n">
-        <v>-11000</v>
+        <v>-28000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>투자 경고 종목 지정 후 주가 하락. 단주치기 및 개미 꼬시기 의혹 제기.</t>
+          <t>급락 및 하한가 가능성 언급. 선수 이탈 및 신용 물량 털기에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['투자경고', '주가 하락', '단주치기']</t>
+          <t>['급락', '하한가', '신용']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>201490</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_13.xlsx
+++ b/data/trending_integrated_20260922_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
         <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52298268090</v>
+        <v>52333536290</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5430992624</v>
+        <v>5432253369</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65300</v>
+        <v>65400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.86%</t>
+          <t>'+25.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>162227618950</v>
+        <v>163005743500</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13620</v>
+        <v>13560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+22.48%</t>
+          <t>'+21.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F5" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -877,7 +877,7 @@
         <v>11270</v>
       </c>
       <c r="L5" t="n">
-        <v>13680</v>
+        <v>13840</v>
       </c>
       <c r="M5" t="n">
         <v>10810</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>188495856190</v>
+        <v>206823031015</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가스터빈 관련 대미 투자 소식에도 불구하고 주가 하한가 및 급락세. 이해 불가 의견.</t>
+          <t>대미 투자 1호 확정 관련 속보 확인. 가스터빈 대장주로서 주가 상승 기대감과 함께 일부 부정적인 전망도 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가스터빈', '대미 투자', '주가 급락']</t>
+          <t>['대미 투자', '가스터빈', '속보']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112800</v>
+        <v>112700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.70%</t>
+          <t>'+10.60%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>284784836850</v>
+        <v>287220769850</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31950</v>
+        <v>31100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.58%</t>
+          <t>'+7.80%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.62</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>195</v>
+        <v>308</v>
       </c>
       <c r="H7" t="n">
-        <v>11.3</v>
+        <v>52.41</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>29700</v>
+        <v>28850</v>
       </c>
       <c r="K7" t="n">
-        <v>30500</v>
+        <v>29250</v>
       </c>
       <c r="L7" t="n">
-        <v>33450</v>
+        <v>31200</v>
       </c>
       <c r="M7" t="n">
-        <v>30000</v>
+        <v>29150</v>
       </c>
       <c r="N7" t="n">
-        <v>11.92</v>
+        <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>248839143675</v>
+        <v>136929159800</v>
       </c>
       <c r="P7" t="n">
-        <v>75900</v>
+        <v>31200</v>
       </c>
       <c r="Q7" t="n">
-        <v>15000</v>
+        <v>21000</v>
       </c>
       <c r="R7" t="n">
-        <v>207000</v>
+        <v>872000</v>
       </c>
       <c r="S7" t="n">
-        <v>7000</v>
+        <v>265000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 전력 수요 증가에 따른 주목 가능성 언급. 단기 상승 기대감 있으나 전고점 돌파 난항.</t>
+          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 전력', '거래량', '전고점']</t>
+          <t>['국제유가', '환율', '매수세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30950</v>
+        <v>31950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.28%</t>
+          <t>'+7.58%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>283</v>
+        <v>201</v>
       </c>
       <c r="H8" t="n">
-        <v>52.2</v>
+        <v>11.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,143 +1147,143 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28850</v>
+        <v>29700</v>
       </c>
       <c r="K8" t="n">
-        <v>29250</v>
+        <v>30500</v>
       </c>
       <c r="L8" t="n">
-        <v>31000</v>
+        <v>33450</v>
       </c>
       <c r="M8" t="n">
-        <v>29150</v>
+        <v>30000</v>
       </c>
       <c r="N8" t="n">
-        <v>25.79</v>
+        <v>11.92</v>
       </c>
       <c r="O8" t="n">
-        <v>119708024450</v>
+        <v>250861730550</v>
       </c>
       <c r="P8" t="n">
-        <v>31200</v>
+        <v>75900</v>
       </c>
       <c r="Q8" t="n">
-        <v>21000</v>
+        <v>15000</v>
       </c>
       <c r="R8" t="n">
-        <v>872000</v>
+        <v>207000</v>
       </c>
       <c r="S8" t="n">
-        <v>265000</v>
+        <v>7000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
+          <t>AI 전력 수요 증가에 따른 주목 가능성 언급. 단기 상승 기대감 있으나 전고점 돌파 난항.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국제유가', '환율', '매수세']</t>
+          <t>['AI 전력', '거래량', '전고점']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6120</v>
+        <v>19180</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.44%</t>
+          <t>'+4.87%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G9" t="n">
-        <v>142</v>
+        <v>677</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5860</v>
+        <v>18290</v>
       </c>
       <c r="K9" t="n">
-        <v>6200</v>
+        <v>18830</v>
       </c>
       <c r="L9" t="n">
-        <v>6610</v>
+        <v>19540</v>
       </c>
       <c r="M9" t="n">
-        <v>6080</v>
+        <v>18540</v>
       </c>
       <c r="N9" t="n">
-        <v>0.19</v>
+        <v>10.74</v>
       </c>
       <c r="O9" t="n">
-        <v>65088238130</v>
+        <v>137407561535</v>
       </c>
       <c r="P9" t="n">
-        <v>13140</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>3725</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-259000</v>
+        <v>146000</v>
       </c>
       <c r="S9" t="n">
-        <v>34000</v>
+        <v>41000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>가상화폐 테마 강세 및 비트코인 급등에 따른 수혜 기대. 공매도 세력에 대한 언급.</t>
+          <t>공매도 관련 의혹 제기 및 감사원 신고 완료 언급. 시장 조성자 및 공매도 구조에 대한 비판과 함께 주가 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['가상화폐', '비트코인', '공매도']</t>
+          <t>['공매도', '감사원', '시세조종']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19030</v>
+        <v>6110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.05%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.27</v>
+        <v>-0.19</v>
       </c>
       <c r="E10" t="n">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>676</v>
+        <v>142</v>
       </c>
       <c r="H10" t="n">
-        <v>10.47</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18290</v>
+        <v>5860</v>
       </c>
       <c r="K10" t="n">
-        <v>18830</v>
+        <v>6200</v>
       </c>
       <c r="L10" t="n">
-        <v>19540</v>
+        <v>6610</v>
       </c>
       <c r="M10" t="n">
-        <v>18540</v>
+        <v>6080</v>
       </c>
       <c r="N10" t="n">
-        <v>10.74</v>
+        <v>0.19</v>
       </c>
       <c r="O10" t="n">
-        <v>131028749915</v>
+        <v>65402796815</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>13140</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>3725</v>
       </c>
       <c r="R10" t="n">
-        <v>146000</v>
+        <v>-259000</v>
       </c>
       <c r="S10" t="n">
-        <v>41000</v>
+        <v>34000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 관련 이슈 및 감사원 신고 완료 내용 언급. 연기금 매수세 유입.</t>
+          <t>가상화폐 테마 강세 및 비트코인 급등에 따른 수혜 기대. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '감사원', '연기금']</t>
+          <t>['가상화폐', '비트코인', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,99 +1384,99 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6490</v>
+        <v>87900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.85%</t>
+          <t>'+3.05%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>366</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>203</v>
       </c>
       <c r="G11" t="n">
-        <v>163</v>
+        <v>1288</v>
       </c>
       <c r="H11" t="n">
-        <v>4.86</v>
+        <v>23.05</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6310</v>
+        <v>85300</v>
       </c>
       <c r="K11" t="n">
-        <v>6460</v>
+        <v>87000</v>
       </c>
       <c r="L11" t="n">
-        <v>7090</v>
+        <v>88100</v>
       </c>
       <c r="M11" t="n">
-        <v>6350</v>
+        <v>85200</v>
       </c>
       <c r="N11" t="n">
-        <v>4.95</v>
+        <v>23.12</v>
       </c>
       <c r="O11" t="n">
-        <v>51322655710</v>
+        <v>180354570600</v>
       </c>
       <c r="P11" t="n">
-        <v>11760</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>1620</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-74000</v>
+        <v>-240000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>대미 투자 1호 확정 소식과 함께 SMR 추진 및 가스터빈 기술에 대한 긍정적 전망. 공매도 세력에 대한 비판과 함께 주가 상승 기대감 고조.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['대미 투자', 'SMR', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>213500</v>
+        <v>214000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.64%</t>
+          <t>'+2.88%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H12" t="n">
         <v>75.5</v>
@@ -1530,7 +1530,7 @@
         <v>75.44</v>
       </c>
       <c r="O12" t="n">
-        <v>699419643000</v>
+        <v>711926279250</v>
       </c>
       <c r="P12" t="n">
         <v>243500</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>326250</v>
+        <v>327000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.43%</t>
+          <t>'+2.67%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F13" t="n">
         <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H13" t="n">
         <v>3.22</v>
@@ -1622,7 +1622,7 @@
         <v>3.62</v>
       </c>
       <c r="O13" t="n">
-        <v>111843025250</v>
+        <v>113116153000</v>
       </c>
       <c r="P13" t="n">
         <v>635000</v>
@@ -1667,92 +1667,92 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13260</v>
+        <v>13700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.31%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>335</v>
+        <v>502</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12960</v>
+        <v>13400</v>
       </c>
       <c r="K14" t="n">
-        <v>13500</v>
+        <v>13630</v>
       </c>
       <c r="L14" t="n">
-        <v>14190</v>
+        <v>13800</v>
       </c>
       <c r="M14" t="n">
-        <v>13250</v>
+        <v>13180</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>20948970515</v>
+        <v>56225499165</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-46000</v>
+        <v>-91000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 관련 뉴스 언급. 원전주로서 주가 상승 기대감과 함께 일부 부정적인 전망도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['SMR', '웨스팅하우스', '원전주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G15" t="n">
-        <v>2107</v>
+        <v>2071</v>
       </c>
       <c r="H15" t="n">
         <v>46.56</v>
@@ -1806,7 +1806,7 @@
         <v>46.46</v>
       </c>
       <c r="O15" t="n">
-        <v>2821530929500</v>
+        <v>2913585972250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 낙관론 및 배당 기대감에 따른 주가 상승 전망. 외인 및 기관 매수세 유입.</t>
+          <t>AI 낙관론에 따른 주가 상승 기대감과 배당금 기대감이 혼재. 외인 및 기관 순매수 동향 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13760</v>
+        <v>13220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.62%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>176</v>
+        <v>336</v>
       </c>
       <c r="H16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13540</v>
+        <v>12960</v>
       </c>
       <c r="K16" t="n">
-        <v>13870</v>
+        <v>13500</v>
       </c>
       <c r="L16" t="n">
-        <v>14650</v>
+        <v>14190</v>
       </c>
       <c r="M16" t="n">
-        <v>13740</v>
+        <v>13210</v>
       </c>
       <c r="N16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>91988064445</v>
+        <v>21343319695</v>
       </c>
       <c r="P16" t="n">
-        <v>20300</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>2885</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>8000</v>
+        <v>-46000</v>
       </c>
       <c r="S16" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86600</v>
+        <v>13810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.52%</t>
+          <t>'+1.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>1231</v>
+        <v>197</v>
       </c>
       <c r="H17" t="n">
-        <v>23.05</v>
+        <v>3.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,235 +1975,235 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85300</v>
+        <v>13540</v>
       </c>
       <c r="K17" t="n">
-        <v>87000</v>
+        <v>13870</v>
       </c>
       <c r="L17" t="n">
-        <v>87500</v>
+        <v>14650</v>
       </c>
       <c r="M17" t="n">
-        <v>85200</v>
+        <v>13740</v>
       </c>
       <c r="N17" t="n">
-        <v>23.12</v>
+        <v>3.68</v>
       </c>
       <c r="O17" t="n">
-        <v>158866750250</v>
+        <v>92707518995</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>20300</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>2885</v>
       </c>
       <c r="R17" t="n">
-        <v>-240000</v>
+        <v>8000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>13000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 SMR(소형모듈원자로) 사업 추진 확정. 공급 계약 체결 및 주가 상승 기대.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '미국 투자', '공급 계약']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1886000</v>
+        <v>6430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
-        <v>486</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>2121</v>
+        <v>168</v>
       </c>
       <c r="H18" t="n">
-        <v>50.17</v>
+        <v>4.86</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1868000</v>
+        <v>6310</v>
       </c>
       <c r="K18" t="n">
-        <v>1909000</v>
+        <v>6460</v>
       </c>
       <c r="L18" t="n">
-        <v>1935000</v>
+        <v>7090</v>
       </c>
       <c r="M18" t="n">
-        <v>1882000</v>
+        <v>6350</v>
       </c>
       <c r="N18" t="n">
-        <v>50.23</v>
+        <v>4.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3313319364000</v>
+        <v>51916962580</v>
       </c>
       <c r="P18" t="n">
-        <v>2987000</v>
+        <v>11760</v>
       </c>
       <c r="Q18" t="n">
-        <v>333000</v>
+        <v>1620</v>
       </c>
       <c r="R18" t="n">
-        <v>44000</v>
+        <v>-74000</v>
       </c>
       <c r="S18" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>AI 수요 증가에 따른 SK하이닉스 주가 상승 기대. 200 돌파 및 25만원 목표.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['AI', 'SK하이닉스', '자사주 매수']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17790</v>
+        <v>1883000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.68</v>
+        <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>175</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>101</v>
+        <v>481</v>
       </c>
       <c r="G19" t="n">
-        <v>762</v>
+        <v>2037</v>
       </c>
       <c r="H19" t="n">
-        <v>6.22</v>
+        <v>50.17</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17720</v>
+        <v>1868000</v>
       </c>
       <c r="K19" t="n">
-        <v>18230</v>
+        <v>1909000</v>
       </c>
       <c r="L19" t="n">
-        <v>18750</v>
+        <v>1935000</v>
       </c>
       <c r="M19" t="n">
-        <v>17500</v>
+        <v>1882000</v>
       </c>
       <c r="N19" t="n">
-        <v>7.9</v>
+        <v>50.23</v>
       </c>
       <c r="O19" t="n">
-        <v>146385102450</v>
+        <v>3437025208500</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R19" t="n">
-        <v>-494000</v>
+        <v>44000</v>
       </c>
       <c r="S19" t="n">
-        <v>14000</v>
+        <v>31000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
+          <t>주가 200 돌파 및 230-240까지의 상승 여력에 대한 기대감 표출. 일부 매물대 및 차트 분석 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '실적', '추세']</t>
+          <t>['반도체', 'AI', '200돌파']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10590</v>
+        <v>17770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="G20" t="n">
-        <v>178</v>
+        <v>766</v>
       </c>
       <c r="H20" t="n">
-        <v>9.609999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,60 +2251,60 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10550</v>
+        <v>17720</v>
       </c>
       <c r="K20" t="n">
-        <v>10730</v>
+        <v>18230</v>
       </c>
       <c r="L20" t="n">
-        <v>11160</v>
+        <v>18750</v>
       </c>
       <c r="M20" t="n">
-        <v>10300</v>
+        <v>17500</v>
       </c>
       <c r="N20" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>128914328750</v>
+        <v>147939292395</v>
       </c>
       <c r="P20" t="n">
-        <v>11640</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>3735</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>215000</v>
+        <v>-494000</v>
       </c>
       <c r="S20" t="n">
-        <v>-478000</v>
+        <v>14000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['광통신', '실적', '추세']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8490</v>
+        <v>8510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="H21" t="n">
         <v>26.58</v>
@@ -2358,7 +2358,7 @@
         <v>26.57</v>
       </c>
       <c r="O21" t="n">
-        <v>17944816395</v>
+        <v>18261704420</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 부진에 대한 논의. 반도체 늪, 무능한 회사라는 평가.</t>
+          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '주가 부진', '재무 실적']</t>
+          <t>['SMR', '대미 투자', '가스터빈']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21400</v>
+        <v>10520</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>1.01</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>21500</v>
+        <v>10550</v>
       </c>
       <c r="K22" t="n">
-        <v>21200</v>
+        <v>10730</v>
       </c>
       <c r="L22" t="n">
-        <v>22900</v>
+        <v>11160</v>
       </c>
       <c r="M22" t="n">
-        <v>20850</v>
+        <v>10300</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>8.6</v>
       </c>
       <c r="O22" t="n">
-        <v>50387222300</v>
+        <v>130885006010</v>
       </c>
       <c r="P22" t="n">
-        <v>22900</v>
+        <v>11640</v>
       </c>
       <c r="Q22" t="n">
-        <v>9900</v>
+        <v>3735</v>
       </c>
       <c r="R22" t="n">
-        <v>79000</v>
+        <v>215000</v>
       </c>
       <c r="S22" t="n">
-        <v>-8000</v>
+        <v>-478000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24100</v>
+        <v>21400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.41</v>
+        <v>-0.05</v>
       </c>
       <c r="E23" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H23" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,143 +2527,143 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>25250</v>
+        <v>21500</v>
       </c>
       <c r="K23" t="n">
-        <v>26150</v>
+        <v>21200</v>
       </c>
       <c r="L23" t="n">
-        <v>26600</v>
+        <v>22900</v>
       </c>
       <c r="M23" t="n">
-        <v>23800</v>
+        <v>20850</v>
       </c>
       <c r="N23" t="n">
-        <v>0.35</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>98553079125</v>
+        <v>50732842775</v>
       </c>
       <c r="P23" t="n">
-        <v>39350</v>
+        <v>22900</v>
       </c>
       <c r="Q23" t="n">
-        <v>8200</v>
+        <v>9900</v>
       </c>
       <c r="R23" t="n">
-        <v>16000</v>
+        <v>79000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 임상 FDA 관련 기대감 있으나, 단기 변동성 및 재무 상태에 대한 우려.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['FDA', '임상', '재무']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10400</v>
+        <v>24200</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.97%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.4</v>
+        <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F24" t="n">
         <v>59</v>
       </c>
       <c r="G24" t="n">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="H24" t="n">
-        <v>17.89</v>
+        <v>1.76</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>11060</v>
+        <v>25250</v>
       </c>
       <c r="K24" t="n">
-        <v>10570</v>
+        <v>26150</v>
       </c>
       <c r="L24" t="n">
-        <v>10815</v>
+        <v>26600</v>
       </c>
       <c r="M24" t="n">
-        <v>10060</v>
+        <v>23800</v>
       </c>
       <c r="N24" t="n">
-        <v>18.29</v>
+        <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>37930908415</v>
+        <v>99087573025</v>
       </c>
       <c r="P24" t="n">
-        <v>22450</v>
+        <v>39350</v>
       </c>
       <c r="Q24" t="n">
-        <v>1760</v>
+        <v>8200</v>
       </c>
       <c r="R24" t="n">
-        <v>-11000</v>
+        <v>16000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 주가 하락세. 조급해하지 말라는 의견.</t>
+          <t>미국 임상 FDA 관련 기대감 있으나, 단기 변동성 및 재무 상태에 대한 우려.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['투경', '단주치기', '주가 하락']</t>
+          <t>['FDA', '임상', '재무']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,97 +2672,189 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3810</v>
+        <v>10370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-6.04%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F25" t="n">
         <v>59</v>
       </c>
       <c r="G25" t="n">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="H25" t="n">
-        <v>0.96</v>
+        <v>17.89</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4055</v>
+        <v>11060</v>
       </c>
       <c r="K25" t="n">
-        <v>4080</v>
+        <v>10570</v>
       </c>
       <c r="L25" t="n">
-        <v>4080</v>
+        <v>10815</v>
       </c>
       <c r="M25" t="n">
-        <v>3810</v>
+        <v>10060</v>
       </c>
       <c r="N25" t="n">
-        <v>0.33</v>
+        <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>10794555732</v>
+        <v>38290096330</v>
       </c>
       <c r="P25" t="n">
-        <v>6480</v>
+        <v>22450</v>
       </c>
       <c r="Q25" t="n">
-        <v>1738</v>
+        <v>1760</v>
       </c>
       <c r="R25" t="n">
-        <v>-28000</v>
+        <v>-11000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>급락 및 하한가 가능성 언급. 선수 이탈 및 신용 물량 털기에 대한 부정적 전망.</t>
+          <t>투자경고 종목 지정 가능성 언급 및 주가 하락 우려. 단주치기 등 비정상적인 거래 방식에 대한 의혹 제기.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>['투자경고', '단주치기', '하락']</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3777</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>'-6.86%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E26" t="n">
+        <v>94</v>
+      </c>
+      <c r="F26" t="n">
+        <v>61</v>
+      </c>
+      <c r="G26" t="n">
+        <v>302</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>4055</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4080</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4080</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3777</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O26" t="n">
+        <v>11251431727</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6480</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-28000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>급락 및 하한가 가능성 언급. 선수 이탈 및 신용 물량 털기에 대한 부정적 전망.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
         <v>0.1</v>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>['급락', '하한가', '신용']</t>
         </is>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>5</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>201490</t>
         </is>

--- a/data/trending_integrated_20260922_13.xlsx
+++ b/data/trending_integrated_20260922_13.xlsx
@@ -581,7 +581,7 @@
         <v>141</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
         <v>323</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52333536290</v>
+        <v>52350448790</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스에 따른 급등. 기술력 및 잭팟급 재료 언급.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스 기반 주가 급등. 7배 초가속 등 기술력에 대한 기대감. 빅테크 기업과의 연관성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
+          <t>['NPU', '휴머노이드', 'AI반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5432253369</v>
+        <v>5433026549</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65400</v>
+        <v>13900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.05%</t>
+          <t>'+25.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>111</v>
+        <v>403</v>
       </c>
       <c r="H4" t="n">
-        <v>6.87</v>
+        <v>0.62</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>52300</v>
+        <v>11120</v>
       </c>
       <c r="K4" t="n">
-        <v>60800</v>
+        <v>11270</v>
       </c>
       <c r="L4" t="n">
-        <v>67900</v>
+        <v>13970</v>
       </c>
       <c r="M4" t="n">
-        <v>59700</v>
+        <v>10810</v>
       </c>
       <c r="N4" t="n">
-        <v>6.88</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>163005743500</v>
+        <v>218286541040</v>
       </c>
       <c r="P4" t="n">
-        <v>148300</v>
+        <v>20850</v>
       </c>
       <c r="Q4" t="n">
-        <v>16300</v>
+        <v>4020</v>
       </c>
       <c r="R4" t="n">
-        <v>-15000</v>
+        <v>-24000</v>
       </c>
       <c r="S4" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브로드컴 투자 공급 계약 관련 긍정적 반응. 키 맞추기 및 이격 축소 기대.</t>
+          <t>상한가 가능성 언급에도 불구하고 급락 및 사기꾼 언급 등 부정적 전망. 대미투자 관련 뉴스가 있으나 불확실성 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['브로드컴', '공급 계약', '키 맞추기']</t>
+          <t>['급락', '사기꾼', '대미투자']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13560</v>
+        <v>65300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.94%</t>
+          <t>'+24.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>395</v>
+        <v>112</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62</v>
+        <v>6.87</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11120</v>
+        <v>52300</v>
       </c>
       <c r="K5" t="n">
-        <v>11270</v>
+        <v>60800</v>
       </c>
       <c r="L5" t="n">
-        <v>13840</v>
+        <v>67900</v>
       </c>
       <c r="M5" t="n">
-        <v>10810</v>
+        <v>59700</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>6.88</v>
       </c>
       <c r="O5" t="n">
-        <v>206823031015</v>
+        <v>164543399150</v>
       </c>
       <c r="P5" t="n">
-        <v>20850</v>
+        <v>148300</v>
       </c>
       <c r="Q5" t="n">
-        <v>4020</v>
+        <v>16300</v>
       </c>
       <c r="R5" t="n">
-        <v>-24000</v>
+        <v>-15000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대미 투자 1호 확정 관련 속보 확인. 가스터빈 대장주로서 주가 상승 기대감과 함께 일부 부정적인 전망도 혼재.</t>
+          <t>브로드컴 투자 공급 계약 관련 긍정적 반응. 키 맞추기 및 이격 축소 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대미 투자', '가스터빈', '속보']</t>
+          <t>['브로드컴', '공급 계약', '키 맞추기']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112700</v>
+        <v>112600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.60%</t>
+          <t>'+10.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
         <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>287220769850</v>
+        <v>290710724850</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,27 +1027,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31100</v>
+        <v>31050</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.80%</t>
+          <t>'+7.63%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="H7" t="n">
-        <v>52.41</v>
+        <v>52.43</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>136929159800</v>
+        <v>141420457375</v>
       </c>
       <c r="P7" t="n">
         <v>31200</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31950</v>
+        <v>31850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.58%</t>
+          <t>'+7.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
         <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H8" t="n">
         <v>11.3</v>
@@ -1162,7 +1162,7 @@
         <v>11.92</v>
       </c>
       <c r="O8" t="n">
-        <v>250861730550</v>
+        <v>255546145200</v>
       </c>
       <c r="P8" t="n">
         <v>75900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 전력 수요 증가에 따른 주목 가능성 언급. 단기 상승 기대감 있으나 전고점 돌파 난항.</t>
+          <t>단기 3만 5천원 가능성 언급. AI 전력수요 증가에 따른 기대감. 가온전선과의 비교 및 주가 부진에 대한 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 전력', '거래량', '전고점']</t>
+          <t>['AI', '전력수요', '거래량']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19180</v>
+        <v>6090</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.87%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.27</v>
+        <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>677</v>
+        <v>142</v>
       </c>
       <c r="H9" t="n">
-        <v>10.47</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18290</v>
+        <v>5860</v>
       </c>
       <c r="K9" t="n">
-        <v>18830</v>
+        <v>6200</v>
       </c>
       <c r="L9" t="n">
-        <v>19540</v>
+        <v>6610</v>
       </c>
       <c r="M9" t="n">
-        <v>18540</v>
+        <v>6080</v>
       </c>
       <c r="N9" t="n">
-        <v>10.74</v>
+        <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>137407561535</v>
+        <v>65757542105</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>13140</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>3725</v>
       </c>
       <c r="R9" t="n">
-        <v>146000</v>
+        <v>-259000</v>
       </c>
       <c r="S9" t="n">
-        <v>41000</v>
+        <v>34000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 관련 의혹 제기 및 감사원 신고 완료 언급. 시장 조성자 및 공매도 구조에 대한 비판과 함께 주가 상승 기대감 표출.</t>
+          <t>가상화폐 테마 강세 및 비트코인 급등에 따른 수혜 기대. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '감사원', '시세조종']</t>
+          <t>['가상화폐', '비트코인', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6110</v>
+        <v>18945</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+3.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>142</v>
+        <v>707</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>10.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5860</v>
+        <v>18290</v>
       </c>
       <c r="K10" t="n">
-        <v>6200</v>
+        <v>18830</v>
       </c>
       <c r="L10" t="n">
-        <v>6610</v>
+        <v>19540</v>
       </c>
       <c r="M10" t="n">
-        <v>6080</v>
+        <v>18540</v>
       </c>
       <c r="N10" t="n">
-        <v>0.19</v>
+        <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>65402796815</v>
+        <v>141469622730</v>
       </c>
       <c r="P10" t="n">
-        <v>13140</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3725</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-259000</v>
+        <v>146000</v>
       </c>
       <c r="S10" t="n">
-        <v>34000</v>
+        <v>41000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>가상화폐 테마 강세 및 비트코인 급등에 따른 수혜 기대. 공매도 세력에 대한 언급.</t>
+          <t>공매도 세력에 대한 강한 비판과 함께 주가 상승 기대감. 감사원 신고, 대차 오링 등 공매도 관련 근거 제시. 원전 사업 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['가상화폐', '비트코인', '공매도']</t>
+          <t>['공매도', '원전', '대차']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87900</v>
+        <v>325500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.05%</t>
+          <t>'+2.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>366</v>
+        <v>116</v>
       </c>
       <c r="F11" t="n">
-        <v>203</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>1288</v>
+        <v>283</v>
       </c>
       <c r="H11" t="n">
-        <v>23.05</v>
+        <v>3.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>85300</v>
+        <v>318500</v>
       </c>
       <c r="K11" t="n">
-        <v>87000</v>
+        <v>333000</v>
       </c>
       <c r="L11" t="n">
-        <v>88100</v>
+        <v>349500</v>
       </c>
       <c r="M11" t="n">
-        <v>85200</v>
+        <v>322500</v>
       </c>
       <c r="N11" t="n">
-        <v>23.12</v>
+        <v>3.62</v>
       </c>
       <c r="O11" t="n">
-        <v>180354570600</v>
+        <v>116132965750</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>635000</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>52600</v>
       </c>
       <c r="R11" t="n">
-        <v>-240000</v>
+        <v>-7000</v>
       </c>
       <c r="S11" t="n">
-        <v>-8000</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대미 투자 1호 확정 소식과 함께 SMR 추진 및 가스터빈 기술에 대한 긍정적 전망. 공매도 세력에 대한 비판과 함께 주가 상승 기대감 고조.</t>
+          <t>신고가 경신 및 52주 신고가 구간 진입. 텍사스 가스복합발전 프로젝트 수혜 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대미 투자', 'SMR', '공매도']</t>
+          <t>['신고가', '가스복합발전', '프로젝트']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214000</v>
+        <v>212500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.88%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H12" t="n">
         <v>75.5</v>
@@ -1530,7 +1530,7 @@
         <v>75.44</v>
       </c>
       <c r="O12" t="n">
-        <v>711926279250</v>
+        <v>737574406500</v>
       </c>
       <c r="P12" t="n">
         <v>243500</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>327000</v>
+        <v>86900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.67%</t>
+          <t>'+1.88%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.4</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>383</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>207</v>
       </c>
       <c r="G13" t="n">
-        <v>279</v>
+        <v>1371</v>
       </c>
       <c r="H13" t="n">
-        <v>3.22</v>
+        <v>23.05</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>318500</v>
+        <v>85300</v>
       </c>
       <c r="K13" t="n">
-        <v>333000</v>
+        <v>87000</v>
       </c>
       <c r="L13" t="n">
-        <v>349500</v>
+        <v>88100</v>
       </c>
       <c r="M13" t="n">
-        <v>325000</v>
+        <v>85200</v>
       </c>
       <c r="N13" t="n">
-        <v>3.62</v>
+        <v>23.12</v>
       </c>
       <c r="O13" t="n">
-        <v>113116153000</v>
+        <v>191830428500</v>
       </c>
       <c r="P13" t="n">
-        <v>635000</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>52600</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-7000</v>
+        <v>-240000</v>
       </c>
       <c r="S13" t="n">
-        <v>5000</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>신고가 경신 및 52주 신고가 구간 진입. 텍사스 가스복합발전 프로젝트 수혜 기대.</t>
+          <t>대미 투자(SMR, 원전) 관련 공급 계약 체결 및 추진 확정 소식. 주가 급등 기대감 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['신고가', '가스복합발전', '프로젝트']</t>
+          <t>['대미투자', 'SMR', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,99 +1660,99 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13700</v>
+        <v>13200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+1.85%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>502</v>
+        <v>352</v>
       </c>
       <c r="H14" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13400</v>
+        <v>12960</v>
       </c>
       <c r="K14" t="n">
-        <v>13630</v>
+        <v>13500</v>
       </c>
       <c r="L14" t="n">
-        <v>13800</v>
+        <v>14190</v>
       </c>
       <c r="M14" t="n">
-        <v>13180</v>
+        <v>13200</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>56225499165</v>
+        <v>21546326725</v>
       </c>
       <c r="P14" t="n">
-        <v>30200</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>3540</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-91000</v>
+        <v>-46000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 관련 뉴스 언급. 원전주로서 주가 상승 기대감과 함께 일부 부정적인 전망도 존재.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SMR', '웨스팅하우스', '원전주']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>279750</v>
+        <v>279000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.10%</t>
+          <t>'+1.82%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G15" t="n">
-        <v>2071</v>
+        <v>2030</v>
       </c>
       <c r="H15" t="n">
         <v>46.56</v>
@@ -1806,7 +1806,7 @@
         <v>46.46</v>
       </c>
       <c r="O15" t="n">
-        <v>2913585972250</v>
+        <v>3008306763750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 낙관론에 따른 주가 상승 기대감과 배당금 기대감이 혼재. 외인 및 기관 순매수 동향 확인.</t>
+          <t>AI 낙관론에 따른 주가 상승 기대감. 배당금 관련 논의와 함께 30만원 돌파 전망. 외인·기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1851,70 +1851,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13220</v>
+        <v>6400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+1.43%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>336</v>
+        <v>167</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>12960</v>
+        <v>6310</v>
       </c>
       <c r="K16" t="n">
-        <v>13500</v>
+        <v>6460</v>
       </c>
       <c r="L16" t="n">
-        <v>14190</v>
+        <v>7090</v>
       </c>
       <c r="M16" t="n">
-        <v>13210</v>
+        <v>6350</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="O16" t="n">
-        <v>21343319695</v>
+        <v>52516593060</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>11760</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>1620</v>
       </c>
       <c r="R16" t="n">
-        <v>-46000</v>
+        <v>-74000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13810</v>
+        <v>13710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.99%</t>
+          <t>'+1.26%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
         <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H17" t="n">
         <v>3.34</v>
@@ -1984,13 +1984,13 @@
         <v>14650</v>
       </c>
       <c r="M17" t="n">
-        <v>13740</v>
+        <v>13710</v>
       </c>
       <c r="N17" t="n">
         <v>3.68</v>
       </c>
       <c r="O17" t="n">
-        <v>92707518995</v>
+        <v>93766932525</v>
       </c>
       <c r="P17" t="n">
         <v>20300</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6430</v>
+        <v>13540</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.90%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.09</v>
+        <v>-0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>168</v>
+        <v>514</v>
       </c>
       <c r="H18" t="n">
-        <v>4.86</v>
+        <v>5.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,60 +2067,60 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6310</v>
+        <v>13400</v>
       </c>
       <c r="K18" t="n">
-        <v>6460</v>
+        <v>13630</v>
       </c>
       <c r="L18" t="n">
-        <v>7090</v>
+        <v>13800</v>
       </c>
       <c r="M18" t="n">
-        <v>6350</v>
+        <v>13180</v>
       </c>
       <c r="N18" t="n">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>51916962580</v>
+        <v>61020485950</v>
       </c>
       <c r="P18" t="n">
-        <v>11760</v>
+        <v>30200</v>
       </c>
       <c r="Q18" t="n">
-        <v>1620</v>
+        <v>3540</v>
       </c>
       <c r="R18" t="n">
-        <v>-74000</v>
+        <v>-91000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['SMR', '웨스팅하우스', '원전']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1883000</v>
+        <v>1873000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="G19" t="n">
-        <v>2037</v>
+        <v>1918</v>
       </c>
       <c r="H19" t="n">
         <v>50.17</v>
@@ -2168,13 +2168,13 @@
         <v>1935000</v>
       </c>
       <c r="M19" t="n">
-        <v>1882000</v>
+        <v>1871000</v>
       </c>
       <c r="N19" t="n">
         <v>50.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3437025208500</v>
+        <v>3595306973000</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 200 돌파 및 230-240까지의 상승 여력에 대한 기대감 표출. 일부 매물대 및 차트 분석 언급.</t>
+          <t>230-240까지 상승 전망 속에서 개미들의 매도와 주가 하락에 대한 불만. 단기 이익 실현 및 매물대 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '200돌파']</t>
+          <t>['개미', '매물대', '단타']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17770</v>
+        <v>17740</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F20" t="n">
         <v>101</v>
       </c>
       <c r="G20" t="n">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="H20" t="n">
         <v>6.22</v>
@@ -2266,7 +2266,7 @@
         <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>147939292395</v>
+        <v>150629114745</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2326,13 +2326,13 @@
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F21" t="n">
         <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H21" t="n">
         <v>26.58</v>
@@ -2358,7 +2358,7 @@
         <v>26.57</v>
       </c>
       <c r="O21" t="n">
-        <v>18261704420</v>
+        <v>18505543270</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10520</v>
+        <v>21400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="H22" t="n">
-        <v>9.609999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10550</v>
+        <v>21500</v>
       </c>
       <c r="K22" t="n">
-        <v>10730</v>
+        <v>21200</v>
       </c>
       <c r="L22" t="n">
-        <v>11160</v>
+        <v>22900</v>
       </c>
       <c r="M22" t="n">
-        <v>10300</v>
+        <v>20850</v>
       </c>
       <c r="N22" t="n">
-        <v>8.6</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>130885006010</v>
+        <v>51024248925</v>
       </c>
       <c r="P22" t="n">
-        <v>11640</v>
+        <v>22900</v>
       </c>
       <c r="Q22" t="n">
-        <v>3735</v>
+        <v>9900</v>
       </c>
       <c r="R22" t="n">
-        <v>215000</v>
+        <v>79000</v>
       </c>
       <c r="S22" t="n">
-        <v>-478000</v>
+        <v>-8000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21400</v>
+        <v>10440</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-1.04%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.05</v>
+        <v>1.01</v>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,38 +2527,38 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>21500</v>
+        <v>10550</v>
       </c>
       <c r="K23" t="n">
-        <v>21200</v>
+        <v>10730</v>
       </c>
       <c r="L23" t="n">
-        <v>22900</v>
+        <v>11160</v>
       </c>
       <c r="M23" t="n">
-        <v>20850</v>
+        <v>10300</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>8.6</v>
       </c>
       <c r="O23" t="n">
-        <v>50732842775</v>
+        <v>133670242165</v>
       </c>
       <c r="P23" t="n">
-        <v>22900</v>
+        <v>11640</v>
       </c>
       <c r="Q23" t="n">
-        <v>9900</v>
+        <v>3735</v>
       </c>
       <c r="R23" t="n">
-        <v>79000</v>
+        <v>215000</v>
       </c>
       <c r="S23" t="n">
-        <v>-8000</v>
+        <v>-478000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24200</v>
+        <v>24100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F24" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G24" t="n">
         <v>224</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>99087573025</v>
+        <v>99753027100</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10370</v>
+        <v>10410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-6.24%</t>
+          <t>'-5.88%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F25" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>38290096330</v>
+        <v>38729930430</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3777</v>
+        <v>3755</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-6.86%</t>
+          <t>'-7.40%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F26" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G26" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H26" t="n">
         <v>0.96</v>
@@ -2812,13 +2812,13 @@
         <v>4080</v>
       </c>
       <c r="M26" t="n">
-        <v>3777</v>
+        <v>3745</v>
       </c>
       <c r="N26" t="n">
         <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>11251431727</v>
+        <v>11821242698</v>
       </c>
       <c r="P26" t="n">
         <v>6480</v>

--- a/data/trending_integrated_20260922_13.xlsx
+++ b/data/trending_integrated_20260922_13.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F2" t="n">
         <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52350448790</v>
+        <v>52392211390</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스 기반 주가 급등. 7배 초가속 등 기술력에 대한 기대감. 빅테크 기업과의 연관성 언급.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 및 AI 반도체 파트너십 뉴스 기반 급등 기대. 기술력 우수 평가.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5433026549</v>
+        <v>5445316649</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13900</v>
+        <v>65200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.00%</t>
+          <t>'+24.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>403</v>
+        <v>114</v>
       </c>
       <c r="H4" t="n">
-        <v>0.62</v>
+        <v>6.87</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11120</v>
+        <v>52300</v>
       </c>
       <c r="K4" t="n">
-        <v>11270</v>
+        <v>60800</v>
       </c>
       <c r="L4" t="n">
-        <v>13970</v>
+        <v>67900</v>
       </c>
       <c r="M4" t="n">
-        <v>10810</v>
+        <v>59700</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>218286541040</v>
+        <v>166958938100</v>
       </c>
       <c r="P4" t="n">
-        <v>20850</v>
+        <v>148300</v>
       </c>
       <c r="Q4" t="n">
-        <v>4020</v>
+        <v>16300</v>
       </c>
       <c r="R4" t="n">
-        <v>-24000</v>
+        <v>-15000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>상한가 가능성 언급에도 불구하고 급락 및 사기꾼 언급 등 부정적 전망. 대미투자 관련 뉴스가 있으나 불확실성 존재.</t>
+          <t>브로드컴 투자 공급 계약 뉴스 기반 상승 기대. 20일선 안착 여부 및 키 맞추기 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['급락', '사기꾼', '대미투자']</t>
+          <t>['공급계약', '20일선', '키맞추기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65300</v>
+        <v>13760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+24.86%</t>
+          <t>'+23.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
-        <v>112</v>
+        <v>430</v>
       </c>
       <c r="H5" t="n">
-        <v>6.87</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>52300</v>
+        <v>11120</v>
       </c>
       <c r="K5" t="n">
-        <v>60800</v>
+        <v>11270</v>
       </c>
       <c r="L5" t="n">
-        <v>67900</v>
+        <v>14140</v>
       </c>
       <c r="M5" t="n">
-        <v>59700</v>
+        <v>10810</v>
       </c>
       <c r="N5" t="n">
-        <v>6.88</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>164543399150</v>
+        <v>235604353440</v>
       </c>
       <c r="P5" t="n">
-        <v>148300</v>
+        <v>20850</v>
       </c>
       <c r="Q5" t="n">
-        <v>16300</v>
+        <v>4020</v>
       </c>
       <c r="R5" t="n">
-        <v>-15000</v>
+        <v>-24000</v>
       </c>
       <c r="S5" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>브로드컴 투자 공급 계약 관련 긍정적 반응. 키 맞추기 및 이격 축소 기대.</t>
+          <t>상한가 가능성 언급에도 불구하고 급락 및 사기꾼 언급 등 부정적 전망. 대미투자 관련 뉴스가 있으나 불확실성 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['브로드컴', '공급 계약', '키 맞추기']</t>
+          <t>['급락', '사기꾼', '대미투자']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112600</v>
+        <v>112100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.50%</t>
+          <t>'+10.01%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>290710724850</v>
+        <v>296145687050</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31050</v>
+        <v>31150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.63%</t>
+          <t>'+7.97%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="H7" t="n">
         <v>52.43</v>
@@ -1070,7 +1070,7 @@
         <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>141420457375</v>
+        <v>147647670900</v>
       </c>
       <c r="P7" t="n">
         <v>31200</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31850</v>
+        <v>31900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.24%</t>
+          <t>'+7.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H8" t="n">
         <v>11.3</v>
@@ -1162,7 +1162,7 @@
         <v>11.92</v>
       </c>
       <c r="O8" t="n">
-        <v>255546145200</v>
+        <v>258759038925</v>
       </c>
       <c r="P8" t="n">
         <v>75900</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6090</v>
+        <v>6040</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1248,13 +1248,13 @@
         <v>6610</v>
       </c>
       <c r="M9" t="n">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="N9" t="n">
         <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>65757542105</v>
+        <v>66610661985</v>
       </c>
       <c r="P9" t="n">
         <v>13140</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>가상화폐 테마 강세 및 비트코인 급등에 따른 수혜 기대. 공매도 세력에 대한 언급.</t>
+          <t>비트코인 급등에 따른 가상화폐 테마 상승 기대감. 업비트 상장 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['가상화폐', '비트코인', '공매도']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18945</v>
+        <v>18840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.58%</t>
+          <t>'+3.01%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="H10" t="n">
         <v>10.47</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>141469622730</v>
+        <v>146128050430</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>325500</v>
+        <v>212500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.20%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.4</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="H11" t="n">
-        <v>3.22</v>
+        <v>75.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>318500</v>
+        <v>208000</v>
       </c>
       <c r="K11" t="n">
-        <v>333000</v>
+        <v>215000</v>
       </c>
       <c r="L11" t="n">
-        <v>349500</v>
+        <v>216000</v>
       </c>
       <c r="M11" t="n">
-        <v>322500</v>
+        <v>211000</v>
       </c>
       <c r="N11" t="n">
-        <v>3.62</v>
+        <v>75.44</v>
       </c>
       <c r="O11" t="n">
-        <v>116132965750</v>
+        <v>763696662000</v>
       </c>
       <c r="P11" t="n">
-        <v>635000</v>
+        <v>243500</v>
       </c>
       <c r="Q11" t="n">
-        <v>52600</v>
+        <v>64700</v>
       </c>
       <c r="R11" t="n">
-        <v>-7000</v>
+        <v>-683000</v>
       </c>
       <c r="S11" t="n">
-        <v>5000</v>
+        <v>-90000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>신고가 경신 및 52주 신고가 구간 진입. 텍사스 가스복합발전 프로젝트 수혜 기대.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['신고가', '가스복합발전', '프로젝트']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>212500</v>
+        <v>86700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.16%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>394</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>212</v>
       </c>
       <c r="G12" t="n">
-        <v>340</v>
+        <v>1422</v>
       </c>
       <c r="H12" t="n">
-        <v>75.5</v>
+        <v>23.05</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>208000</v>
+        <v>85300</v>
       </c>
       <c r="K12" t="n">
-        <v>215000</v>
+        <v>87000</v>
       </c>
       <c r="L12" t="n">
-        <v>216000</v>
+        <v>88100</v>
       </c>
       <c r="M12" t="n">
-        <v>211000</v>
+        <v>85200</v>
       </c>
       <c r="N12" t="n">
-        <v>75.44</v>
+        <v>23.12</v>
       </c>
       <c r="O12" t="n">
-        <v>737574406500</v>
+        <v>199120875800</v>
       </c>
       <c r="P12" t="n">
-        <v>243500</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>64700</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-683000</v>
+        <v>-240000</v>
       </c>
       <c r="S12" t="n">
-        <v>-90000</v>
+        <v>-8000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>미국 투자 관련 공급 계약 체결 및 SMR 추진 확정 뉴스 기반 기대감. 공매도에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['공급계약', 'SMR', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>86900</v>
+        <v>278000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.88%</t>
+          <t>'+1.46%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>383</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>207</v>
+        <v>480</v>
       </c>
       <c r="G13" t="n">
-        <v>1371</v>
+        <v>2013</v>
       </c>
       <c r="H13" t="n">
-        <v>23.05</v>
+        <v>46.56</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>85300</v>
+        <v>274000</v>
       </c>
       <c r="K13" t="n">
-        <v>87000</v>
+        <v>283000</v>
       </c>
       <c r="L13" t="n">
-        <v>88100</v>
+        <v>283500</v>
       </c>
       <c r="M13" t="n">
-        <v>85200</v>
+        <v>277500</v>
       </c>
       <c r="N13" t="n">
-        <v>23.12</v>
+        <v>46.46</v>
       </c>
       <c r="O13" t="n">
-        <v>191830428500</v>
+        <v>3168043833500</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>81100</v>
       </c>
       <c r="R13" t="n">
-        <v>-240000</v>
+        <v>550000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>307000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대미 투자(SMR, 원전) 관련 공급 계약 체결 및 추진 확정 소식. 주가 급등 기대감 및 공매도 관련 언급.</t>
+          <t>AI 낙관론 기반 주가 상승 기대감 및 배당 기대감 존재. 단기적인 주가 방향성에 대한 의견 분분.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대미투자', 'SMR', '공매도']</t>
+          <t>['AI', '배당금', '주가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13200</v>
+        <v>13140</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.85%</t>
+          <t>'+1.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1708,13 +1708,13 @@
         <v>14190</v>
       </c>
       <c r="M14" t="n">
-        <v>13200</v>
+        <v>13120</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>21546326725</v>
+        <v>21967444350</v>
       </c>
       <c r="P14" t="n">
         <v>19380</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>279000</v>
+        <v>322500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.82%</t>
+          <t>'+1.26%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>122</v>
       </c>
       <c r="F15" t="n">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>2030</v>
+        <v>289</v>
       </c>
       <c r="H15" t="n">
-        <v>46.56</v>
+        <v>3.22</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>274000</v>
+        <v>318500</v>
       </c>
       <c r="K15" t="n">
-        <v>283000</v>
+        <v>333000</v>
       </c>
       <c r="L15" t="n">
-        <v>283500</v>
+        <v>349500</v>
       </c>
       <c r="M15" t="n">
-        <v>278500</v>
+        <v>321000</v>
       </c>
       <c r="N15" t="n">
-        <v>46.46</v>
+        <v>3.62</v>
       </c>
       <c r="O15" t="n">
-        <v>3008306763750</v>
+        <v>118306666500</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>635000</v>
       </c>
       <c r="Q15" t="n">
-        <v>81100</v>
+        <v>52600</v>
       </c>
       <c r="R15" t="n">
-        <v>550000</v>
+        <v>-7000</v>
       </c>
       <c r="S15" t="n">
-        <v>307000</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 낙관론에 따른 주가 상승 기대감. 배당금 관련 논의와 함께 30만원 돌파 전망. 외인·기관 매수세 유입.</t>
+          <t>신고가 경신 및 52주 신고가 구간 진입. 텍사스 가스복합발전 프로젝트 수혜 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '배당금', '낙관론']</t>
+          <t>['신고가', '가스복합발전', '프로젝트']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6400</v>
+        <v>13700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.43%</t>
+          <t>'+1.18%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.09</v>
+        <v>-0.34</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="H16" t="n">
-        <v>4.86</v>
+        <v>3.34</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6310</v>
+        <v>13540</v>
       </c>
       <c r="K16" t="n">
-        <v>6460</v>
+        <v>13870</v>
       </c>
       <c r="L16" t="n">
-        <v>7090</v>
+        <v>14650</v>
       </c>
       <c r="M16" t="n">
-        <v>6350</v>
+        <v>13650</v>
       </c>
       <c r="N16" t="n">
-        <v>4.95</v>
+        <v>3.68</v>
       </c>
       <c r="O16" t="n">
-        <v>52516593060</v>
+        <v>95407045205</v>
       </c>
       <c r="P16" t="n">
-        <v>11760</v>
+        <v>20300</v>
       </c>
       <c r="Q16" t="n">
-        <v>1620</v>
+        <v>2885</v>
       </c>
       <c r="R16" t="n">
-        <v>-74000</v>
+        <v>8000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13710</v>
+        <v>6380</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.26%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.34</v>
+        <v>-0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="H17" t="n">
-        <v>3.34</v>
+        <v>4.86</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13540</v>
+        <v>6310</v>
       </c>
       <c r="K17" t="n">
-        <v>13870</v>
+        <v>6460</v>
       </c>
       <c r="L17" t="n">
-        <v>14650</v>
+        <v>7090</v>
       </c>
       <c r="M17" t="n">
-        <v>13710</v>
+        <v>6350</v>
       </c>
       <c r="N17" t="n">
-        <v>3.68</v>
+        <v>4.95</v>
       </c>
       <c r="O17" t="n">
-        <v>93766932525</v>
+        <v>52921534240</v>
       </c>
       <c r="P17" t="n">
-        <v>20300</v>
+        <v>11760</v>
       </c>
       <c r="Q17" t="n">
-        <v>2885</v>
+        <v>1620</v>
       </c>
       <c r="R17" t="n">
-        <v>8000</v>
+        <v>-74000</v>
       </c>
       <c r="S17" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13540</v>
+        <v>13450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="H18" t="n">
         <v>5.02</v>
@@ -2082,7 +2082,7 @@
         <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>61020485950</v>
+        <v>63054423695</v>
       </c>
       <c r="P18" t="n">
         <v>30200</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1873000</v>
+        <v>21550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>474</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>1918</v>
+        <v>227</v>
       </c>
       <c r="H19" t="n">
-        <v>50.17</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1868000</v>
+        <v>21500</v>
       </c>
       <c r="K19" t="n">
-        <v>1909000</v>
+        <v>21200</v>
       </c>
       <c r="L19" t="n">
-        <v>1935000</v>
+        <v>22900</v>
       </c>
       <c r="M19" t="n">
-        <v>1871000</v>
+        <v>20850</v>
       </c>
       <c r="N19" t="n">
-        <v>50.23</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3595306973000</v>
+        <v>51500856750</v>
       </c>
       <c r="P19" t="n">
-        <v>2987000</v>
+        <v>22900</v>
       </c>
       <c r="Q19" t="n">
-        <v>333000</v>
+        <v>9900</v>
       </c>
       <c r="R19" t="n">
-        <v>44000</v>
+        <v>79000</v>
       </c>
       <c r="S19" t="n">
-        <v>31000</v>
+        <v>-8000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>230-240까지 상승 전망 속에서 개미들의 매도와 주가 하락에 대한 불만. 단기 이익 실현 및 매물대 언급.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,103 +2199,103 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['개미', '매물대', '단타']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17740</v>
+        <v>1871000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.68</v>
+        <v>-0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>179</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>101</v>
+        <v>472</v>
       </c>
       <c r="G20" t="n">
-        <v>772</v>
+        <v>1811</v>
       </c>
       <c r="H20" t="n">
-        <v>6.22</v>
+        <v>50.17</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17720</v>
+        <v>1868000</v>
       </c>
       <c r="K20" t="n">
-        <v>18230</v>
+        <v>1909000</v>
       </c>
       <c r="L20" t="n">
-        <v>18750</v>
+        <v>1935000</v>
       </c>
       <c r="M20" t="n">
-        <v>17500</v>
+        <v>1864000</v>
       </c>
       <c r="N20" t="n">
-        <v>7.9</v>
+        <v>50.23</v>
       </c>
       <c r="O20" t="n">
-        <v>150629114745</v>
+        <v>3813769331000</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q20" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R20" t="n">
-        <v>-494000</v>
+        <v>44000</v>
       </c>
       <c r="S20" t="n">
-        <v>14000</v>
+        <v>31000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
+          <t>주가 하락세 및 외국인 매수세 대비 개인 매도 물량에 대한 부정적 인식. 전강후강 패턴 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '실적', '추세']</t>
+          <t>['주가', '외국인', '개인']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8510</v>
+        <v>8500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2332,7 +2332,7 @@
         <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H21" t="n">
         <v>26.58</v>
@@ -2358,7 +2358,7 @@
         <v>26.57</v>
       </c>
       <c r="O21" t="n">
-        <v>18505543270</v>
+        <v>18738380040</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21400</v>
+        <v>17670</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>-1.68</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="G22" t="n">
-        <v>221</v>
+        <v>788</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2</v>
+        <v>6.22</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,60 +2435,60 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>21500</v>
+        <v>17720</v>
       </c>
       <c r="K22" t="n">
-        <v>21200</v>
+        <v>18230</v>
       </c>
       <c r="L22" t="n">
-        <v>22900</v>
+        <v>18750</v>
       </c>
       <c r="M22" t="n">
-        <v>20850</v>
+        <v>17500</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>7.9</v>
       </c>
       <c r="O22" t="n">
-        <v>51024248925</v>
+        <v>154134353230</v>
       </c>
       <c r="P22" t="n">
-        <v>22900</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>9900</v>
+        <v>1272</v>
       </c>
       <c r="R22" t="n">
-        <v>79000</v>
+        <v>-494000</v>
       </c>
       <c r="S22" t="n">
-        <v>-8000</v>
+        <v>14000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['광통신', '실적', '추세']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10440</v>
+        <v>10410</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.04%</t>
+          <t>'-1.33%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H23" t="n">
         <v>9.609999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>8.6</v>
       </c>
       <c r="O23" t="n">
-        <v>133670242165</v>
+        <v>137137061710</v>
       </c>
       <c r="P23" t="n">
         <v>11640</v>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24100</v>
+        <v>23700</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-6.14%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G24" t="n">
         <v>224</v>
@@ -2628,13 +2628,13 @@
         <v>26600</v>
       </c>
       <c r="M24" t="n">
-        <v>23800</v>
+        <v>23550</v>
       </c>
       <c r="N24" t="n">
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>99753027100</v>
+        <v>104804137575</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2679,70 +2679,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10410</v>
+        <v>3780</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-6.78%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E25" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G25" t="n">
-        <v>259</v>
+        <v>322</v>
       </c>
       <c r="H25" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K25" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L25" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M25" t="n">
-        <v>10060</v>
+        <v>3735</v>
       </c>
       <c r="N25" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O25" t="n">
-        <v>38729930430</v>
+        <v>12185721833</v>
       </c>
       <c r="P25" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q25" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R25" t="n">
-        <v>-11000</v>
+        <v>-28000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 가능성 언급 및 주가 하락 우려. 단주치기 등 비정상적인 거래 방식에 대한 의혹 제기.</t>
+          <t>텐베거 기대감 속 급락 및 신규 매수 개미 몰살 우려. 차트상 말아 올리는 패턴 기대.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['투자경고', '단주치기', '하락']</t>
+          <t>['텐베거', '차트분석', '급락']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,77 +2764,77 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3755</v>
+        <v>10310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-7.40%</t>
+          <t>'-6.78%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E26" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F26" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>301</v>
+        <v>253</v>
       </c>
       <c r="H26" t="n">
-        <v>0.96</v>
+        <v>17.89</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4055</v>
+        <v>11060</v>
       </c>
       <c r="K26" t="n">
-        <v>4080</v>
+        <v>10570</v>
       </c>
       <c r="L26" t="n">
-        <v>4080</v>
+        <v>10815</v>
       </c>
       <c r="M26" t="n">
-        <v>3745</v>
+        <v>10060</v>
       </c>
       <c r="N26" t="n">
-        <v>0.33</v>
+        <v>18.29</v>
       </c>
       <c r="O26" t="n">
-        <v>11821242698</v>
+        <v>39374180145</v>
       </c>
       <c r="P26" t="n">
-        <v>6480</v>
+        <v>22450</v>
       </c>
       <c r="Q26" t="n">
-        <v>1738</v>
+        <v>1760</v>
       </c>
       <c r="R26" t="n">
-        <v>-28000</v>
+        <v>-11000</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>급락 및 하한가 가능성 언급. 선수 이탈 및 신용 물량 털기에 대한 부정적 전망.</t>
+          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['급락', '하한가', '신용']</t>
+          <t>['투자경고', '단주치기', '주가']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
